--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513259_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513259_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4536</v>
+        <v>5.4211</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9644</v>
+        <v>4.7301</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4892</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>2.8688</v>
@@ -610,13 +610,13 @@
         <v>1.9825</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1548</v>
+        <v>0.1222</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4013</v>
+        <v>0.167</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2465</v>
+        <v>-0.0448</v>
       </c>
       <c r="V2" t="n">
         <v>0.4476</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7683</v>
+        <v>1.7087</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8477</v>
+        <v>1.7401</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0794</v>
+        <v>-0.0313</v>
       </c>
       <c r="G3" t="n">
         <v>1.2393</v>
@@ -688,13 +688,13 @@
         <v>1.7622</v>
       </c>
       <c r="S3" t="n">
-        <v>1.987</v>
+        <v>0.9275</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0995</v>
+        <v>0.9919</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1124</v>
+        <v>-0.0644</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1189</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0611</v>
+        <v>1.6144</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4607</v>
+        <v>-0.1092</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5217</v>
+        <v>1.7235</v>
       </c>
       <c r="G4" t="n">
         <v>-2.1987</v>
@@ -766,13 +766,13 @@
         <v>1.5419</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3701</v>
+        <v>0.1832</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1686</v>
+        <v>0.5201</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5387</v>
+        <v>-0.3369</v>
       </c>
       <c r="V4" t="n">
         <v>4.2906</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5308</v>
+        <v>0.6924</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9429</v>
+        <v>-0.2794</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4121</v>
+        <v>0.9718</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0288</v>
+        <v>2.5348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5474</v>
+        <v>1.2111</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5185999999999999</v>
+        <v>1.3238</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9966</v>
+        <v>3.8493</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8447</v>
+        <v>0.2905</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1519</v>
+        <v>3.5589</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9678</v>
+        <v>-1.3145</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2973</v>
+        <v>0.9206</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6705</v>
+        <v>-2.2351</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.8811</v>
+        <v>-3.0838</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1014</v>
+        <v>-5.5068</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2203</v>
+        <v>2.423</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1911</v>
+        <v>0.2343</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2562</v>
+        <v>0.2592</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4473</v>
+        <v>-0.0248</v>
       </c>
       <c r="V5" t="n">
-        <v>1.192</v>
+        <v>1.007</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3039</v>
+        <v>1.1189</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1119</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0747</v>
+        <v>0.5057</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0464</v>
+        <v>1.1773</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9718</v>
+        <v>-0.6715</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5348</v>
+        <v>0.0288</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2111</v>
+        <v>0.5474</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3238</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8493</v>
+        <v>0.9966</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2905</v>
+        <v>0.8447</v>
       </c>
       <c r="L6" t="n">
-        <v>3.5589</v>
+        <v>0.1519</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3145</v>
+        <v>-0.9678</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9206</v>
+        <v>-0.2973</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2351</v>
+        <v>-0.6705</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.0838</v>
+        <v>-0.8811</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.5068</v>
+        <v>-1.1014</v>
       </c>
       <c r="R6" t="n">
-        <v>2.423</v>
+        <v>0.2203</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5327</v>
+        <v>0.166</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5079</v>
+        <v>-0.0219</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0248</v>
+        <v>0.1879</v>
       </c>
       <c r="V6" t="n">
-        <v>1.007</v>
+        <v>1.192</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1189</v>
+        <v>1.3039</v>
       </c>
       <c r="X6" t="n">
         <v>-0.1119</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6289</v>
+        <v>-0.6847</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7296</v>
+        <v>-1.6125</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1007</v>
+        <v>0.9278</v>
       </c>
       <c r="G7" t="n">
         <v>0.2549</v>
@@ -1000,13 +1000,13 @@
         <v>0.8811</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1554</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3281</v>
+        <v>-0.211</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2285</v>
+        <v>0.0556</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5639</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4611</v>
+        <v>-1.6898</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3537</v>
+        <v>-2.2365</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.5467</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6004</v>
@@ -1078,13 +1078,13 @@
         <v>1.3216</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2335</v>
+        <v>0.0047</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5203</v>
+        <v>-0.4031</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7538</v>
+        <v>0.4079</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4158</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2198</v>
+        <v>-3.1194</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3009</v>
+        <v>0.2672</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5207</v>
+        <v>-3.3866</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4016</v>
+        <v>0.2969</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4908</v>
+        <v>1.6312</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.8924</v>
+        <v>-1.3343</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7006</v>
+        <v>1.7155</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1632</v>
+        <v>0.4134</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.8638</v>
+        <v>1.3021</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.701</v>
+        <v>-1.4186</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3276</v>
+        <v>1.2179</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0286</v>
+        <v>-2.6365</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7622</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>-1.1014</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.1014</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.5116000000000001</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.3469</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.1647</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-2.9047</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.7622</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.402</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.8165</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.4145</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-2.9823</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.185</v>
-      </c>
       <c r="X9" t="n">
-        <v>-3.1673</v>
+        <v>-2.9047</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1728</v>
+        <v>-3.7384</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3826</v>
+        <v>-1.2754</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7902</v>
+        <v>-2.463</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2969</v>
+        <v>-3.4016</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6312</v>
+        <v>0.4908</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3343</v>
+        <v>-3.8924</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7155</v>
+        <v>-2.7006</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4134</v>
+        <v>0.1632</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3021</v>
+        <v>-2.8638</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4186</v>
+        <v>-0.701</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2179</v>
+        <v>0.3276</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.6365</v>
+        <v>-1.0286</v>
       </c>
       <c r="P10" t="n">
+        <v>1.7622</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.1014</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.1014</v>
+        <v>1.7622</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.565</v>
+        <v>0.8834</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9968</v>
+        <v>1.2403</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5683</v>
+        <v>-0.3569</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.9047</v>
+        <v>-2.9823</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.9047</v>
+        <v>-3.1673</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.478</v>
+        <v>-6.5631</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.4898</v>
+        <v>-9.4885</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0119</v>
+        <v>2.9254</v>
       </c>
       <c r="G11" t="n">
         <v>-5.9607</v>
@@ -1312,13 +1312,13 @@
         <v>1.3216</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8387</v>
+        <v>0.0761</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7687</v>
+        <v>0.2327</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0701</v>
+        <v>-0.1565</v>
       </c>
       <c r="V11" t="n">
         <v>1.3039</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.221499999999999</v>
+        <v>-5.853100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.406899999999998</v>
+        <v>-7.0868</v>
       </c>
       <c r="F12" t="n">
-        <v>1.185499999999999</v>
+        <v>1.2338</v>
       </c>
       <c r="G12" t="n">
         <v>-5.9379</v>
       </c>
       <c r="H12" t="n">
-        <v>3.435099999999999</v>
+        <v>3.4351</v>
       </c>
       <c r="I12" t="n">
         <v>-9.3729</v>
@@ -1378,7 +1378,7 @@
         <v>6.0476</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.387600000000001</v>
+        <v>-8.387600000000003</v>
       </c>
       <c r="P12" t="n">
         <v>-1.1014</v>
@@ -1390,16 +1390,16 @@
         <v>14.3178</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5623</v>
+        <v>1.9304</v>
       </c>
       <c r="T12" t="n">
-        <v>2.107899999999999</v>
+        <v>2.4283</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5457</v>
+        <v>-0.4976</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7444999999999986</v>
+        <v>-0.7444999999999995</v>
       </c>
       <c r="W12" t="n">
         <v>9.501800000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0325</v>
+        <v>6.0511</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4296</v>
+        <v>4.0782</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6028</v>
+        <v>1.9729</v>
       </c>
       <c r="G13" t="n">
         <v>2.8358</v>
@@ -1468,13 +1468,13 @@
         <v>1.1014</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7914</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7294</v>
+        <v>0.378</v>
       </c>
       <c r="U13" t="n">
-        <v>0.062</v>
+        <v>0.432</v>
       </c>
       <c r="V13" t="n">
         <v>1.3039</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9945</v>
+        <v>3.4496</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8611</v>
+        <v>2.2753</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1334</v>
+        <v>1.1743</v>
       </c>
       <c r="G14" t="n">
         <v>0.9361</v>
@@ -1546,13 +1546,13 @@
         <v>1.9825</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1971</v>
+        <v>-0.742</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5654</v>
+        <v>-0.0204</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7625</v>
+        <v>-0.7216</v>
       </c>
       <c r="V14" t="n">
         <v>1.4934</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>S. MICOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3875</v>
+        <v>3.0117</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5232</v>
+        <v>1.3352</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8643</v>
+        <v>1.6765</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6562</v>
+        <v>2.261</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4046</v>
+        <v>1.2857</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7484</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.85</v>
+        <v>1.5509</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3727</v>
+        <v>0.3954</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4773</v>
+        <v>1.1555</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1938</v>
+        <v>0.71</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0319</v>
+        <v>0.8903</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2257</v>
+        <v>-0.1803</v>
       </c>
       <c r="P15" t="n">
         <v>1.9825</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2203</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2027</v>
+        <v>1.9825</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6868</v>
+        <v>0.0722</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4746</v>
+        <v>-0.2157</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2122</v>
+        <v>0.2879</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3745</v>
+        <v>-1.3039</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1189</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7444</v>
+        <v>-1.3039</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1182</v>
+        <v>2.5236</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1391</v>
+        <v>-0.1798</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9791</v>
+        <v>2.7034</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7678</v>
+        <v>-0.6562</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1134</v>
+        <v>-1.4046</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6545</v>
+        <v>0.7484</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.6079</v>
+        <v>-1.85</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6912</v>
+        <v>-1.3727</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.9166</v>
+        <v>-0.4773</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.16</v>
+        <v>1.1938</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5778</v>
+        <v>-0.0319</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7378</v>
+        <v>1.2257</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5419</v>
+        <v>1.9825</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.2203</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7622</v>
+        <v>2.2027</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1063</v>
+        <v>0.8229</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7294</v>
+        <v>0.7716</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3769</v>
+        <v>0.0513</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2378</v>
+        <v>0.3745</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2378</v>
+        <v>1.1189</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.7444</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MICOVIC</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7908</v>
+        <v>2.2423</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3979</v>
+        <v>0.4362</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3929</v>
+        <v>1.8061</v>
       </c>
       <c r="G17" t="n">
-        <v>2.261</v>
+        <v>-1.7678</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2857</v>
+        <v>-0.1134</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9752999999999999</v>
+        <v>-1.6545</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5509</v>
+        <v>-1.6079</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3954</v>
+        <v>-0.6912</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1555</v>
+        <v>-0.9166</v>
       </c>
       <c r="M17" t="n">
-        <v>0.71</v>
+        <v>-0.16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8903</v>
+        <v>0.5778</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1803</v>
+        <v>-0.7378</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9825</v>
+        <v>1.5419</v>
       </c>
       <c r="Q17" t="n">
+        <v>-0.2203</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.7622</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2039</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.2378</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.2378</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.9825</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-1.1487</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-1.153</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-1.3039</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-1.3039</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.61</v>
+        <v>1.9611</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3265</v>
+        <v>1.1466</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2835</v>
+        <v>0.8145</v>
       </c>
       <c r="G18" t="n">
         <v>3.197</v>
@@ -1858,13 +1858,13 @@
         <v>1.3216</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8248</v>
+        <v>-0.4737</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7406</v>
+        <v>0.0796</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0842</v>
+        <v>-0.5533</v>
       </c>
       <c r="V18" t="n">
         <v>0.5595</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0018</v>
+        <v>1.0629</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8268</v>
+        <v>1.7641</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8286</v>
+        <v>-0.7012</v>
       </c>
       <c r="G19" t="n">
         <v>2.743</v>
@@ -1936,13 +1936,13 @@
         <v>0.8811</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8284</v>
+        <v>0.2363</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7406</v>
+        <v>0.1967</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0878</v>
+        <v>0.0395</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3745</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0876</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0556</v>
+        <v>-0.9384</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0321</v>
+        <v>0.0256</v>
       </c>
       <c r="G20" t="n">
         <v>-0.998</v>
@@ -2014,13 +2014,13 @@
         <v>0.2203</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0897</v>
+        <v>0.0851</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1281</v>
+        <v>-0.0109</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0384</v>
+        <v>0.0961</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4322</v>
+        <v>-3.1685</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3122</v>
+        <v>-3.9399</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.12</v>
+        <v>0.7714</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.101</v>
+        <v>0.8385</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1266</v>
+        <v>0.7755</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9743000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6285</v>
+        <v>0.2225</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7045</v>
+        <v>0.1355</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0759</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4724</v>
+        <v>0.616</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5778</v>
+        <v>0.64</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0503</v>
+        <v>-0.024</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4405</v>
+        <v>-2.6433</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3216</v>
+        <v>-4.846</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8811</v>
+        <v>2.2027</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1463</v>
+        <v>-0.9893</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0124</v>
+        <v>-0.6203</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1587</v>
+        <v>-0.369</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7444</v>
+        <v>-0.3745</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3745</v>
+        <v>1.3039</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.37</v>
+        <v>-1.6784</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7069</v>
+        <v>-3.3969</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4085</v>
+        <v>-3.6637</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7016</v>
+        <v>0.2668</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8385</v>
+        <v>-2.101</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7755</v>
+        <v>-1.1266</v>
       </c>
       <c r="I22" t="n">
-        <v>0.063</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2225</v>
+        <v>-1.6285</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1355</v>
+        <v>-1.7045</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0759</v>
       </c>
       <c r="M22" t="n">
-        <v>0.616</v>
+        <v>-0.4724</v>
       </c>
       <c r="N22" t="n">
-        <v>0.64</v>
+        <v>0.5778</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.024</v>
+        <v>-1.0503</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.6433</v>
+        <v>-0.4405</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.846</v>
+        <v>-1.3216</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2027</v>
+        <v>0.8811</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5277</v>
+        <v>-0.111</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0889</v>
+        <v>-0.3391</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4387</v>
+        <v>0.2281</v>
       </c>
       <c r="V22" t="n">
+        <v>-0.7444</v>
+      </c>
+      <c r="W22" t="n">
         <v>-0.3745</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.3039</v>
-      </c>
       <c r="X22" t="n">
-        <v>-1.6784</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4835</v>
+        <v>-5.0405</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7286</v>
+        <v>-3.3144</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7549</v>
+        <v>-1.7261</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3505</v>
@@ -2248,13 +2248,13 @@
         <v>0.8811</v>
       </c>
       <c r="S23" t="n">
-        <v>0.616</v>
+        <v>0.059</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8857</v>
+        <v>0.2999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2697</v>
+        <v>-0.2409</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4273</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.221499999999998</v>
+        <v>7.783599999999996</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.000700000000001</v>
+        <v>-1.000599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>7.222</v>
+        <v>8.784199999999998</v>
       </c>
       <c r="G24" t="n">
-        <v>5.9379</v>
+        <v>5.937899999999998</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.435099999999999</v>
+        <v>-3.4351</v>
       </c>
       <c r="I24" t="n">
         <v>9.373000000000001</v>
@@ -2302,19 +2302,19 @@
         <v>2.3401</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.047599999999999</v>
+        <v>-6.0476</v>
       </c>
       <c r="L24" t="n">
-        <v>8.387499999999999</v>
+        <v>8.387500000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5977</v>
+        <v>3.597699999999999</v>
       </c>
       <c r="N24" t="n">
         <v>2.6121</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9853000000000004</v>
+        <v>0.9853</v>
       </c>
       <c r="P24" t="n">
         <v>1.101599999999999</v>
@@ -2326,16 +2326,16 @@
         <v>15.4192</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5622</v>
+        <v>-9.999999999983633e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5456999999999995</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.1078</v>
+        <v>-0.5460000000000002</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7444999999999999</v>
+        <v>0.7445000000000004</v>
       </c>
       <c r="W24" t="n">
         <v>10.4312</v>
